--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140240</v>
       </c>
       <c r="B2" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140240</v>
       </c>
       <c r="B2" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140240</v>
       </c>
       <c r="B2" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140240</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140240</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35127-2026 artfynd.xlsx
+++ b/artfynd/A 35127-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137140240</v>
       </c>
       <c r="B2" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137140232</v>
       </c>
       <c r="B3" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
